--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513258_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513258_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4833</v>
+        <v>2.0567</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6395</v>
+        <v>2.4148</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1563</v>
+        <v>-0.3581</v>
       </c>
       <c r="G2" t="n">
         <v>3.5423</v>
@@ -610,13 +610,13 @@
         <v>1.9825</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3152</v>
+        <v>-0.1113</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5746</v>
+        <v>0.3499</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2594</v>
+        <v>-0.4611</v>
       </c>
       <c r="V2" t="n">
         <v>-3.3567</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3756</v>
+        <v>1.8604</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1901</v>
+        <v>0.2849</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5657</v>
+        <v>1.5755</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0503</v>
+        <v>-0.6006</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0042</v>
+        <v>0.8986</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.0544</v>
+        <v>-1.4992</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.6541</v>
+        <v>-0.459</v>
       </c>
       <c r="K3" t="n">
-        <v>2.302</v>
+        <v>1.0162</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.9561</v>
+        <v>-1.4752</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3961</v>
+        <v>-0.1416</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7022</v>
+        <v>-0.1176</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0983</v>
+        <v>-0.024</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3041</v>
+        <v>2.2027</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.3041</v>
+        <v>2.2027</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8782</v>
+        <v>-0.6757</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.536</v>
+        <v>-0.375</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3422</v>
+        <v>-0.3007</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.9339</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1189</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>F. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3516</v>
+        <v>1.8427</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6946</v>
+        <v>2.1995</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3429</v>
+        <v>-0.3569</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5535</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0124</v>
+        <v>0.7328</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5411</v>
+        <v>0.0399</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8586</v>
+        <v>2.7545</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0359</v>
+        <v>0.2103</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8227</v>
+        <v>2.5442</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6949</v>
+        <v>-1.9818</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0235</v>
+        <v>0.5225</v>
       </c>
       <c r="O4" t="n">
-        <v>1.7184</v>
+        <v>-2.5043</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6608000000000001</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.3041</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6608000000000001</v>
+        <v>2.6433</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6249</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1641</v>
+        <v>-0.6031</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4608</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.2378</v>
+        <v>2.4228</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.3523</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2378</v>
+        <v>-0.9294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. ZURBRIGGEN</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0775</v>
+        <v>1.4688</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5497</v>
+        <v>1.8117</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4722</v>
+        <v>-0.3429</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7727000000000001</v>
+        <v>3.5535</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7328</v>
+        <v>0.0124</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0399</v>
+        <v>3.5411</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7545</v>
+        <v>1.8586</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2103</v>
+        <v>0.0359</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5442</v>
+        <v>1.8227</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9818</v>
+        <v>1.6949</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5225</v>
+        <v>-0.0235</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.5043</v>
+        <v>1.7184</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6608000000000001</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.3041</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6433</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.4572</v>
+        <v>-0.5077</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.253</v>
+        <v>-0.0469</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2042</v>
+        <v>-0.4608</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4228</v>
+        <v>-2.2378</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3523</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9294</v>
+        <v>-2.2378</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9863</v>
+        <v>1.4415</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3009</v>
+        <v>-1.0089</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2872</v>
+        <v>2.4504</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6006</v>
+        <v>-1.0503</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8986</v>
+        <v>3.0042</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4992</v>
+        <v>-4.0544</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.459</v>
+        <v>-0.6541</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0162</v>
+        <v>2.302</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4752</v>
+        <v>-2.9561</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1416</v>
+        <v>-0.3961</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1176</v>
+        <v>0.7022</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.024</v>
+        <v>-1.0983</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2027</v>
+        <v>3.3041</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2027</v>
+        <v>3.3041</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5498</v>
+        <v>-0.8123</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9608</v>
+        <v>-0.3548</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5889</v>
+        <v>-0.4575</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9339</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1189</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>T. ROTEGARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.103</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1336</v>
+        <v>0.2101</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1988</v>
+        <v>-0.1072</v>
       </c>
       <c r="G7" t="n">
-        <v>0.178</v>
+        <v>-0.1493</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8778</v>
+        <v>-0.3055</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6999</v>
+        <v>0.1562</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2763</v>
+        <v>0.0539</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.09810000000000001</v>
+        <v>0.0539</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3744</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0983</v>
+        <v>-0.2032</v>
       </c>
       <c r="N7" t="n">
-        <v>0.976</v>
+        <v>-0.3595</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0743</v>
+        <v>0.1562</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1014</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2978</v>
+        <v>0.2523</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0.1562</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3147</v>
+        <v>0.0961</v>
       </c>
       <c r="V7" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3039</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. ROTEGARD</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0453</v>
+        <v>-0.3013</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2101</v>
+        <v>0.0476</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1648</v>
+        <v>-0.3489</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1493</v>
+        <v>0.178</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3055</v>
+        <v>0.8778</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1562</v>
+        <v>-0.6999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0539</v>
+        <v>0.2763</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0539</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.3744</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2032</v>
+        <v>-0.0983</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3595</v>
+        <v>0.976</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1562</v>
+        <v>-1.0743</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1014</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1947</v>
+        <v>-0.6642</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1562</v>
+        <v>-0.4312</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0384</v>
+        <v>-0.233</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.185</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.3039</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>S. LITTLESON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3995</v>
+        <v>-0.5473</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1623</v>
+        <v>-2.0506</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5618</v>
+        <v>1.5032</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7162</v>
+        <v>2.6794</v>
       </c>
       <c r="H9" t="n">
-        <v>4.0106</v>
+        <v>-2.6377</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2944</v>
+        <v>5.3171</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7264</v>
+        <v>2.6737</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6125</v>
+        <v>-2.6915</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1139</v>
+        <v>5.3652</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0102</v>
+        <v>0.0058</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3981</v>
+        <v>0.0538</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4084</v>
+        <v>-0.0481</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.423</v>
+        <v>-1.7622</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.3041</v>
+        <v>-4.4054</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8811</v>
+        <v>2.6433</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0562</v>
+        <v>-0.7201</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4889</v>
+        <v>-0.3188</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4327</v>
+        <v>-0.4013</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7489</v>
+        <v>-0.7444</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7489</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.7444</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. LOBO MARTORELL</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0603</v>
+        <v>-0.5799</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1604</v>
+        <v>-0.3063</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8998</v>
+        <v>-0.2736</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5799</v>
+        <v>2.7162</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2599</v>
+        <v>4.0106</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8397</v>
+        <v>-1.2944</v>
       </c>
       <c r="J10" t="n">
-        <v>0.452</v>
+        <v>3.7264</v>
       </c>
       <c r="K10" t="n">
-        <v>0.018</v>
+        <v>3.6125</v>
       </c>
       <c r="L10" t="n">
-        <v>0.434</v>
+        <v>0.1139</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0319</v>
+        <v>-1.0102</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2419</v>
+        <v>0.3981</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2738</v>
+        <v>-1.4084</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6608000000000001</v>
+        <v>-2.423</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.3041</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.8811</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1412</v>
+        <v>-0.1242</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6124000000000001</v>
+        <v>0.0203</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5288</v>
+        <v>-0.1445</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.7489</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7489</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. LITTLESON</t>
+          <t>J. LOBO MARTORELL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3125</v>
+        <v>-0.799</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7004</v>
+        <v>-0.0433</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3879</v>
+        <v>-0.7557</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6794</v>
+        <v>-0.5799</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.6377</v>
+        <v>0.2599</v>
       </c>
       <c r="I11" t="n">
-        <v>5.3171</v>
+        <v>-0.8397</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6737</v>
+        <v>0.452</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.6915</v>
+        <v>0.018</v>
       </c>
       <c r="L11" t="n">
-        <v>5.3652</v>
+        <v>0.434</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0058</v>
+        <v>-1.0319</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0538</v>
+        <v>0.2419</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0481</v>
+        <v>-1.2738</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7622</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.4054</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6433</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4853</v>
+        <v>-0.8799</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9687</v>
+        <v>-0.4953</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.3847</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7444</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.7444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9169</v>
+        <v>-2.4816</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8079</v>
+        <v>-3.2765</v>
       </c>
       <c r="F12" t="n">
-        <v>0.891</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-1.977</v>
@@ -1390,13 +1390,13 @@
         <v>0.4405</v>
       </c>
       <c r="S12" t="n">
-        <v>0.721</v>
+        <v>0.1562</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4889</v>
+        <v>0.0203</v>
       </c>
       <c r="U12" t="n">
-        <v>0.232</v>
+        <v>0.136</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.695600000000001</v>
+        <v>4.064</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.03710000000000058</v>
+        <v>0.2830000000000004</v>
       </c>
       <c r="F13" t="n">
-        <v>3.7328</v>
+        <v>3.7807</v>
       </c>
       <c r="G13" t="n">
         <v>9.084999999999999</v>
@@ -1444,10 +1444,10 @@
         <v>11.3008</v>
       </c>
       <c r="K13" t="n">
-        <v>4.811800000000002</v>
+        <v>4.8118</v>
       </c>
       <c r="L13" t="n">
-        <v>6.4889</v>
+        <v>6.488899999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-2.2156</v>
@@ -1468,13 +1468,13 @@
         <v>16.5205</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.147300000000001</v>
+        <v>-4.7789</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.3988</v>
+        <v>-2.0784</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.748499999999999</v>
+        <v>-2.7004</v>
       </c>
       <c r="V13" t="n">
         <v>-3.5461</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2139</v>
+        <v>2.3839</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4479</v>
+        <v>-0.1924</v>
       </c>
       <c r="F14" t="n">
-        <v>2.766</v>
+        <v>2.5763</v>
       </c>
       <c r="G14" t="n">
         <v>0.4279</v>
@@ -1546,13 +1546,13 @@
         <v>1.9825</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2311</v>
+        <v>2.4011</v>
       </c>
       <c r="T14" t="n">
-        <v>3.1008</v>
+        <v>1.4605</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1303</v>
+        <v>0.9406</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0045</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,37 +1579,37 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4719</v>
+        <v>1.4554</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6357</v>
+        <v>0.953</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8361</v>
+        <v>0.5024</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.2293</v>
+        <v>-0.4797</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.7912</v>
+        <v>-2.7235</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5619</v>
+        <v>2.2438</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5172</v>
+        <v>0.6075</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.8842</v>
+        <v>-2.4414</v>
       </c>
       <c r="L15" t="n">
-        <v>1.367</v>
+        <v>3.0489</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7121</v>
+        <v>-1.0872</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.907</v>
+        <v>-0.2821</v>
       </c>
       <c r="O15" t="n">
         <v>-0.8051</v>
@@ -1624,28 +1624,28 @@
         <v>0.8811</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4589</v>
+        <v>1.2568</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3557</v>
+        <v>0.5482</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1032</v>
+        <v>0.7085</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6828</v>
+        <v>1.1189</v>
       </c>
       <c r="W15" t="n">
         <v>1.1189</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9719</v>
+        <v>1.2092</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0702</v>
+        <v>2.808</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0983</v>
+        <v>-1.5988</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4797</v>
+        <v>0.9031</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.7235</v>
+        <v>2.0226</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2438</v>
+        <v>-1.1195</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6075</v>
+        <v>2.3936</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.4414</v>
+        <v>2.3282</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0489</v>
+        <v>0.0654</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0872</v>
+        <v>-1.4905</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2821</v>
+        <v>-0.3056</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8051</v>
+        <v>-1.1848</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4405</v>
+        <v>0.4405</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.3216</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8811</v>
+        <v>1.7622</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7732</v>
+        <v>0.61</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6654</v>
+        <v>0.0577</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1078</v>
+        <v>0.5523</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1189</v>
+        <v>-0.7444</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1189</v>
+        <v>1.6784</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.4228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0634</v>
+        <v>1.0036</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4193</v>
+        <v>0.2298</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4827</v>
+        <v>0.7738</v>
       </c>
       <c r="G17" t="n">
-        <v>1.6244</v>
+        <v>-2.2293</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5331</v>
+        <v>-2.7912</v>
       </c>
       <c r="I17" t="n">
-        <v>0.09130000000000001</v>
+        <v>0.5619</v>
       </c>
       <c r="J17" t="n">
-        <v>3.026</v>
+        <v>-0.5172</v>
       </c>
       <c r="K17" t="n">
-        <v>1.995</v>
+        <v>-1.8842</v>
       </c>
       <c r="L17" t="n">
-        <v>1.031</v>
+        <v>1.367</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4016</v>
+        <v>-1.7121</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4619</v>
+        <v>-0.907</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9397</v>
+        <v>-0.8051</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.2027</v>
+        <v>-0.4405</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.4054</v>
+        <v>-1.3216</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2027</v>
+        <v>0.8811</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6623</v>
+        <v>1.9906</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3438</v>
+        <v>0.9497</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3184</v>
+        <v>1.0409</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3039</v>
+        <v>1.6828</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3039</v>
+        <v>1.1189</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.5639</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. MICOVIC</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0209</v>
+        <v>0.89</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.032</v>
+        <v>0.0493</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0529</v>
+        <v>0.8407</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4643</v>
+        <v>1.6244</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2019</v>
+        <v>1.5331</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2624</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.774</v>
+        <v>3.026</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6111</v>
+        <v>1.995</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1629</v>
+        <v>1.031</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.2383</v>
+        <v>-1.4016</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.4619</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4254</v>
+        <v>-0.9397</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2203</v>
+        <v>-2.2027</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1014</v>
+        <v>-4.4054</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3216</v>
+        <v>2.2027</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4839</v>
+        <v>0.1644</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7046</v>
+        <v>0.1248</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2207</v>
+        <v>0.0395</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7489</v>
+        <v>1.3039</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.3039</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>S. MICOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.446</v>
+        <v>0.3166</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7535</v>
+        <v>-0.5633</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1995</v>
+        <v>0.8799</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9031</v>
+        <v>-0.4643</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0226</v>
+        <v>-0.2019</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1195</v>
+        <v>-0.2624</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3936</v>
+        <v>0.774</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3282</v>
+        <v>0.6111</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0654</v>
+        <v>0.1629</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4905</v>
+        <v>-1.2383</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3056</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1848</v>
+        <v>-0.4254</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4405</v>
+        <v>0.2203</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3216</v>
+        <v>-1.1014</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7622</v>
+        <v>1.3216</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0452</v>
+        <v>-0.1882</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9968</v>
+        <v>-0.236</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0484</v>
+        <v>0.0477</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7444</v>
+        <v>0.7489</v>
       </c>
       <c r="W19" t="n">
-        <v>1.6784</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4228</v>
+        <v>0.7489</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5943000000000001</v>
+        <v>-0.5366</v>
       </c>
       <c r="E20" t="n">
         <v>-1.1014</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5071</v>
+        <v>0.5647</v>
       </c>
       <c r="G20" t="n">
         <v>0.4687</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0384</v>
+        <v>0.0961</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0384</v>
+        <v>0.0961</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3266</v>
+        <v>-1.388</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4637</v>
+        <v>-0.698</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8629</v>
+        <v>-0.6899</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7536</v>
@@ -2092,13 +2092,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0488</v>
+        <v>-0.1101</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1405</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1893</v>
+        <v>-0.0163</v>
       </c>
       <c r="V21" t="n">
         <v>-0.185</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.5875</v>
+        <v>-1.8948</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7659</v>
+        <v>-2.4144</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1783</v>
+        <v>0.5196</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4054</v>
@@ -2170,13 +2170,13 @@
         <v>0.8811</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1395</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0405</v>
+        <v>0.392</v>
       </c>
       <c r="U22" t="n">
-        <v>0.099</v>
+        <v>0.4402</v>
       </c>
       <c r="V22" t="n">
         <v>1.1189</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1733</v>
+        <v>-2.4108</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6974</v>
+        <v>-2.8773</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5241</v>
+        <v>0.4664</v>
       </c>
       <c r="G23" t="n">
         <v>-3.263</v>
@@ -2248,13 +2248,13 @@
         <v>1.9825</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7914</v>
+        <v>-0.0289</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9327</v>
+        <v>-0.1126</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1413</v>
+        <v>0.0837</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3099</v>
+        <v>-3.1621</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2794</v>
+        <v>-1.045</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0306</v>
+        <v>-2.117</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9137999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4622</v>
+        <v>-0.3144</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5765</v>
+        <v>-0.3422</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1143</v>
+        <v>0.0278</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4934</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6956</v>
+        <v>-2.1336</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8518</v>
+        <v>-4.851699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>1.155899999999999</v>
+        <v>2.7181</v>
       </c>
       <c r="G25" t="n">
         <v>-9.084999999999999</v>
@@ -2404,13 +2404,13 @@
         <v>13.2164</v>
       </c>
       <c r="S25" t="n">
-        <v>5.1473</v>
+        <v>6.7096</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7485</v>
+        <v>2.7483</v>
       </c>
       <c r="U25" t="n">
-        <v>2.398900000000001</v>
+        <v>3.961</v>
       </c>
       <c r="V25" t="n">
         <v>3.5461</v>
